--- a/i18n/uk.xlsx
+++ b/i18n/uk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -956,6 +956,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Коли інший гравець виконує дію «Отримайте корм»</t>
@@ -965,7 +966,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">, візьміть 1 [invertebrate] </t>
     </r>
@@ -974,6 +976,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t xml:space="preserve">або 1 [fruit] </t>
@@ -983,7 +986,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>з годівниці наприкінці його ходу.</t>
     </r>
@@ -1051,6 +1055,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Оберіть 1-5 птахів у своєму</t>
@@ -1060,7 +1065,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [forest]. Запасіть 1 [seed] зі свого запасу на кожному з них.</t>
     </r>
@@ -1098,6 +1104,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Коли інший гравець виконує дію «Отримайте корм»</t>
@@ -1107,7 +1114,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>, візьміть 1 [seed] з годівниці наприкінці його ходу.</t>
     </r>
@@ -1190,6 +1198,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Візьміть 1 нову карту бонусну. Потім отримайте 1 [die] з годівниці</t>
@@ -1199,7 +1208,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>, покладіть 1 [egg] на будь-якого птаха або візьміть 1 [card].</t>
     </r>
@@ -1600,6 +1610,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Оберіть 1-5 птахів у</t>
@@ -1609,7 +1620,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> своєму [wetland]. Підкладіть 1 [card] з руки під кожного з них. Якщо зробили це, візьміть 1 [card].</t>
     </r>
@@ -1647,6 +1659,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t xml:space="preserve">загального </t>
@@ -1682,6 +1695,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Киньте всі кубик, що знаходяться поза годівницею</t>
@@ -1691,7 +1705,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>. Візьміть із загального запасу стільки [fish], скільки випало [fish], та зробіть запас на цій карті.</t>
     </r>
@@ -2026,6 +2041,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Коли інший гравець з будь-якого приводу підкладає [card], підкладіть 1 [card] з</t>
@@ -2035,7 +2051,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> руки під цього птаха, а потім візьміть 1 [card] наприкінці цього ходу.</t>
     </r>
@@ -2462,6 +2479,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>cavity</t>
@@ -2996,6 +3014,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>nectar</t>
@@ -3083,6 +3102,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>ground</t>
@@ -3170,6 +3190,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>ground</t>
@@ -3431,6 +3452,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>invertebrate</t>
@@ -3448,6 +3470,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>invertebrate</t>
@@ -3505,6 +3528,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>invertebrate</t>
@@ -3541,6 +3565,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>platform</t>
@@ -3860,6 +3885,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>bowl</t>
@@ -4456,14 +4482,12 @@
     <t>VP</t>
   </si>
   <si>
-    <t xml:space="preserve">Анатом </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Птахи</t>
@@ -4473,7 +4497,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>, в назвах яких є частина тіла</t>
     </r>
@@ -4540,14 +4565,12 @@
     <t>Breeding Manager</t>
   </si>
   <si>
-    <t xml:space="preserve">Картограф </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Птахи</t>
@@ -4557,7 +4580,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>, в назвах яких є географічні назви</t>
     </r>
@@ -4629,7 +4653,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>(як-от коричневі, безбарвні, рожеві, бірюзові)&lt;br&gt;</t>
     </r>
@@ -4638,6 +4663,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Птахи без властивостей вважаються безбарвними.</t>
@@ -4667,6 +4693,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Птахи</t>
@@ -4676,7 +4703,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>, в назвах яких є професії, характеристики або заняття людей</t>
     </r>
@@ -4719,14 +4747,12 @@
     <t>Passerine Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Фотограф </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>Птахи</t>
@@ -4736,7 +4762,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>, в назвах яких є кольори</t>
     </r>
@@ -4836,7 +4863,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">: 3[point]; </t>
     </r>
@@ -4855,7 +4883,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">: 5[point]; </t>
     </r>
@@ -4874,7 +4903,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>: 8[point]</t>
     </r>
@@ -4909,7 +4939,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">1 </t>
     </r>
@@ -4928,7 +4959,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> = [bowl] [cavity] [ground] [platform]; </t>
     </r>
@@ -4947,7 +4979,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">: 3[point]; </t>
     </r>
@@ -4966,7 +4999,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>: 8[point]</t>
     </r>
@@ -4976,9 +5010,6 @@
   </si>
   <si>
     <t>Site Selection Expert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Експерт із забудови </t>
   </si>
   <si>
     <t>Колонки, в яких два чи три гнізда – однакового типу:</t>
@@ -4992,7 +5023,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">2 </t>
     </r>
@@ -5011,7 +5043,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">: 1[point]; 3 </t>
     </r>
@@ -5030,7 +5063,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>: 3[point]</t>
     </r>
@@ -5088,9 +5122,6 @@
   </si>
   <si>
     <t>Explanatory Text</t>
-  </si>
-  <si>
-    <t>Bird in Forest</t>
   </si>
   <si>
     <r>
@@ -5098,7 +5129,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[bird] </t>
     </r>
@@ -5107,6 +5139,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>В</t>
@@ -5116,13 +5149,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [forest]</t>
     </r>
-  </si>
-  <si>
-    <t>Bird in Grassland</t>
   </si>
   <si>
     <r>
@@ -5130,7 +5161,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[bird] </t>
     </r>
@@ -5139,6 +5171,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>В</t>
@@ -5148,13 +5181,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [grassland]</t>
     </r>
-  </si>
-  <si>
-    <t>Bird in Wetland</t>
   </si>
   <si>
     <r>
@@ -5162,7 +5193,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[bird] </t>
     </r>
@@ -5171,6 +5203,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>В</t>
@@ -5180,22 +5213,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [wetland]</t>
     </r>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
   </si>
   <si>
     <r>
@@ -5203,7 +5225,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[cavity] [bird] </t>
     </r>
@@ -5212,6 +5235,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>З</t>
@@ -5221,13 +5245,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [egg]</t>
     </r>
-  </si>
-  <si>
-    <t>Bowl Nest Bird with Egg</t>
   </si>
   <si>
     <r>
@@ -5235,7 +5257,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[bowl] [bird] </t>
     </r>
@@ -5244,6 +5267,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>З</t>
@@ -5253,13 +5277,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [egg]</t>
     </r>
-  </si>
-  <si>
-    <t>Ground Nest Bird with Egg</t>
   </si>
   <si>
     <r>
@@ -5267,7 +5289,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[ground] [bird] </t>
     </r>
@@ -5276,6 +5299,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>З</t>
@@ -5285,13 +5309,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [egg]</t>
     </r>
-  </si>
-  <si>
-    <t>Platform Nest Bird with Egg</t>
   </si>
   <si>
     <r>
@@ -5299,7 +5321,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[platform] [bird] </t>
     </r>
@@ -5308,6 +5331,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>З</t>
@@ -5317,36 +5341,16 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [egg]</t>
     </r>
   </si>
   <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
     <t>ВСЬОГО [bird]</t>
   </si>
   <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Корм у запасі</t>
   </si>
   <si>
@@ -5368,9 +5372,6 @@
     <t>Кількість карт птахів у вашій руці.</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
     <t>Птахи, які приносять більше 4 балів</t>
   </si>
   <si>
@@ -5380,9 +5381,6 @@
     <t>Кількість зіграних вами птахів, які приносять більше 4 балів.</t>
   </si>
   <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
     <t>Птахи без яєць</t>
   </si>
   <si>
@@ -5392,9 +5390,6 @@
     <t>Кількість зіграних вами птахів, які не мають яєць на момент підрахунку балів за цю ціль.</t>
   </si>
   <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
     <t>Птахи в одному ряду</t>
   </si>
   <si>
@@ -5404,9 +5399,6 @@
     <t>Кількість зіграних вами птахів у найбільш заселеному ареалі.</t>
   </si>
   <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
     <t>Заповнені колонки</t>
   </si>
   <si>
@@ -5416,18 +5408,12 @@
     <t>Кількість колонок, де всі три клітинки зайняті картами птахів.</t>
   </si>
   <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
     <t>Коричневі властивості</t>
   </si>
   <si>
     <t>Кількість зіграних вами птахів, які мають коричневі властивості «При активації».</t>
   </si>
   <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
     <t>Безбарвні або без властивостей</t>
   </si>
   <si>
@@ -5437,16 +5423,10 @@
     <t>Кількість зіграних вами птахів, які або не мають властивостей, або мають властивості «При розіграші».</t>
   </si>
   <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
     <t>[flocking] ПТАХИ З ПІДКЛАДЕНИМИ КАРТАМИ</t>
   </si>
   <si>
     <t>Кількість зіграних вами птахів, які мають хоча б одну підкладену карту.</t>
-  </si>
-  <si>
-    <t>Food Cost of Played Birds</t>
   </si>
   <si>
     <t>Вартість зіграних птахів у кормі</t>
@@ -5477,9 +5457,6 @@
     <t>Порахуйте вартість у кормі ваших птахів. Враховуйте тільки 1 корм птахам, які мають вибір корму у своїй вартості.</t>
   </si>
   <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>Безхребетні у вартості в кормі ваших птахів.</t>
   </si>
   <si>
@@ -5487,9 +5464,6 @@
   </si>
   <si>
     <t>Порахуйте кількість символів корму у вартості в кормі на картах ваших птахів. Наприклад, для цілі «[fruit]+[seed] у вартості в кормі ваших птахів» продивіться верхні ліві кути карт, що викладені у ваш заповідник, і порахуйте усі [fruit] плюс усі [seed]. Якщо птах має «[fruit]/[seed]» у вартості (ви сплатили АБО при розіграші птаха), для цілі раунду рахується тільки один корм. Не рахуйте [wild] або [nectar].</t>
-  </si>
-  <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
   </si>
   <si>
     <t>Фрукти + зерно у вартості в кормі ваших птахів.</t>
@@ -5500,7 +5474,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[fruit] + [seed] </t>
     </r>
@@ -5509,13 +5484,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>У ВАРТОСТІ В КОРМІ ВАШИХ ПТАХІВ</t>
     </r>
-  </si>
-  <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
   </si>
   <si>
     <t>Гризуни + риба у вартості в кормі ваших птахів.</t>
@@ -5526,7 +5499,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[rodent] + [fish] </t>
     </r>
@@ -5535,15 +5509,13 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>У ВАРТОСТІ В КОРМІ ВАШИХ ПТАХІВ</t>
     </r>
   </si>
   <si>
-    <t>No Goal</t>
-  </si>
-  <si>
     <t>Без цілей</t>
   </si>
   <si>
@@ -5553,9 +5525,6 @@
     <t>Не рахуйте бали наприкінці цього раунду. Збережіть фішку дії. Всі наступні раунди матимуть на 1 дію більше, ніж мали б.</t>
   </si>
   <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
     <t>Дзьоб вказує ліворуч</t>
   </si>
   <si>
@@ -5565,18 +5534,12 @@
     <t>Такі цілі рахують карти з птахами, чий дзьоб повернутий у вказаному напрямку. Птахи, чиї дзьоби спрямовані прямо вперед (або прямо догори), не враховуються для жодної з цих цілей.&lt;br&gt;Ці цілі додали, щоб у гравців був додатковий привід уважніше роздивитися ілюстрації. Хоча ми переглянули всі карти й вирішили, що визначити напрям дзьоба буде не важко, якщо у вас виникнуть із цим труднощі, можете не використовувати ці жетони цілей у грі. Ось декілька карт, для яких потрібні роз’яснення:&lt;br&gt;&lt;ul&gt;&lt;li&gt;Пісочник криводзьобий дивиться вперед, але його дзьоб вказує ліворуч.&lt;/li&gt;&lt;li&gt;На карті гагари полярної (з базової гри) і Little Grebe (з «Крил Азії») два птахи, що дивляться в обидва боки, тож вона враховується для обох цілей.&lt;/li&gt;&lt;li&gt;На карті пірникози великої (з «Крил Європи») два птахи, що дивляться в один бік; вона враховується як одна карта з птахом, що дивиться ліворуч.&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Такі карти птахів не дивляться ані ліворуч, ані праворуч:&lt;br&gt;&lt;b&gt;БАЗОВА ГРА&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Сипуха&lt;/li&gt;&lt;li&gt;Сова неоарктична&lt;/li&gt;&lt;li&gt;Сич американський&lt;/li&gt;&lt;li&gt;Кондор каліфорнійський&lt;/li&gt;&lt;li&gt;Сплюшка північна&lt;/li&gt;&lt;li&gt;Пугач віргінський&lt;/li&gt;&lt;li&gt;Жайворонок рогатий&lt;/li&gt;&lt;li&gt;Сова плямиста&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;ЄВРОПА&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Сич хатній&lt;/li&gt;&lt;li&gt;Сова біла&lt;/li&gt;&lt;li&gt;Підкоришник короткопалий&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;ОКЕАНІЯ&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Еготело австралійський&lt;/li&gt;&lt;li&gt;Какапо&lt;/li&gt;&lt;li&gt;Сова-голконіг руда&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;АЗІЯ&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Bearded Reedling&lt;/li&gt;&lt;li&gt;Eurasian Eagle-Owl&lt;/li&gt;&lt;li&gt;Forest Owlet&lt;/li&gt;&lt;li&gt;Oriental Bay-Owl&lt;/li&gt;&lt;li&gt;Spoon-Billed Sandpiper&lt;/li&gt;&lt;li&gt;Sri Lanka Frogmouth&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
     <t>Дзьоб вказує праворуч</t>
   </si>
   <si>
     <t>[beak-left] ДЗЬОБ ВКАЗУЄ ПРАВОРУЧ</t>
   </si>
   <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
     <t>Фішки на «Зіграйте птаха»</t>
   </si>
   <si>
@@ -5584,9 +5547,6 @@
   </si>
   <si>
     <t>Порахуйте кількість фішок дій, які ви поклали на «Зіграйте птаха» у цьому раунді. Зверніть увагу, що для цього потрібно залишати фішки в рядках, де ви їх зіграли.</t>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
   </si>
   <si>
     <r>
@@ -5594,7 +5554,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[bird] </t>
     </r>
@@ -5612,22 +5573,14 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> ≤3[point]</t>
     </r>
   </si>
   <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
     <t>[duet-token] НА [bowl][cavity][ground][platform]</t>
-  </si>
-  <si>
-    <t>Food Symbols</t>
   </si>
   <si>
     <r>
@@ -5635,7 +5588,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[duet-token] </t>
     </r>
@@ -5644,6 +5598,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>НА</t>
@@ -5653,57 +5608,31 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> [fish][fruit][rodent][seed][invertebrate]</t>
     </r>
   </si>
   <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
     <t>[duet-token] ПО КРАЮ МАПИ</t>
   </si>
   <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
     <t>[duet-token] У БУДЬ-ЯКОМУ ГОРИЗОНТАЛЬНОМУ РЯДУ</t>
   </si>
   <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
     <t>НАЙМЕНШЕ [duet-token] У КОМІРКАХ БОНУСІВ</t>
   </si>
   <si>
-    <t>In Forest</t>
-  </si>
-  <si>
     <t>[duet-token] В [forest]</t>
   </si>
   <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
     <t>[duet-token] В [grassland]</t>
   </si>
   <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
     <t>[duet-token] В [wetland]</t>
   </si>
   <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>ВСЬОГО [duet-token] НА МАПІ</t>
   </si>
   <si>
@@ -5777,6 +5706,153 @@
   </si>
   <si>
     <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Анатом</t>
+  </si>
+  <si>
+    <t>Картограф</t>
+  </si>
+  <si>
+    <t>Фотограф</t>
+  </si>
+  <si>
+    <t>Експерт із забудови</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
   </si>
 </sst>
 </file>
@@ -5798,18 +5874,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -5842,6 +5921,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -5873,19 +5953,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <charset val="238"/>
     </font>
     <font>
@@ -5911,13 +5986,21 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5940,7 +6023,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -5971,14 +6054,15 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -6263,7 +6347,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>1540</v>
+        <v>1491</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -6933,7 +7017,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>1532</v>
+        <v>1483</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>90</v>
@@ -8501,7 +8585,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1533</v>
+        <v>1484</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>294</v>
@@ -9280,7 +9364,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1535</v>
+        <v>1486</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>401</v>
@@ -10170,7 +10254,7 @@
         <v>508</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1536</v>
+        <v>1487</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>13</v>
@@ -12687,7 +12771,7 @@
         <v>838</v>
       </c>
       <c r="F291" s="13" t="s">
-        <v>1539</v>
+        <v>1490</v>
       </c>
       <c r="G291" s="13"/>
       <c r="I291" s="5" t="s">
@@ -12868,7 +12952,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="26" t="s">
-        <v>1538</v>
+        <v>1489</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>864</v>
@@ -13222,7 +13306,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>1534</v>
+        <v>1485</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>924</v>
@@ -15056,7 +15140,7 @@
         <v>1200</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>1537</v>
+        <v>1488</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>1118</v>
@@ -15807,15 +15891,15 @@
         <v>13</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>1305</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>1306</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="16"/>
       <c r="H2" s="15" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75">
@@ -15823,7 +15907,7 @@
         <v>1001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>13</v>
@@ -15839,22 +15923,22 @@
         <v>1002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>1310</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>1311</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="16" t="s">
         <v>1312</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>1313</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -15863,20 +15947,20 @@
         <v>1003</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>1315</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>1316</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="16" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H5" s="5"/>
     </row>
@@ -15885,7 +15969,7 @@
         <v>1004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>13</v>
@@ -15901,7 +15985,7 @@
         <v>1005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>13</v>
@@ -15917,7 +16001,7 @@
         <v>1006</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>13</v>
@@ -15939,15 +16023,15 @@
         <v>13</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1321</v>
+        <v>1493</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="16"/>
       <c r="H9" s="15" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75">
@@ -15955,20 +16039,20 @@
         <v>1008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="16" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H10" s="5"/>
     </row>
@@ -15977,20 +16061,20 @@
         <v>1009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="16" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="H11" s="5"/>
     </row>
@@ -15999,7 +16083,7 @@
         <v>1010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>13</v>
@@ -16015,7 +16099,7 @@
         <v>1011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>13</v>
@@ -16031,22 +16115,22 @@
         <v>1012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F14" s="17" t="s">
         <v>1335</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G14" s="16" t="s">
         <v>1336</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>1337</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>1338</v>
       </c>
       <c r="H14" s="4"/>
     </row>
@@ -16055,7 +16139,7 @@
         <v>1013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>13</v>
@@ -16071,7 +16155,7 @@
         <v>1014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>13</v>
@@ -16087,7 +16171,7 @@
         <v>1015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>13</v>
@@ -16103,7 +16187,7 @@
         <v>1016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>13</v>
@@ -16125,15 +16209,15 @@
         <v>13</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="16"/>
       <c r="H19" s="15" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75">
@@ -16141,7 +16225,7 @@
         <v>1018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>13</v>
@@ -16157,7 +16241,7 @@
         <v>1019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>13</v>
@@ -16173,7 +16257,7 @@
         <v>1020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>13</v>
@@ -16189,7 +16273,7 @@
         <v>1021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>13</v>
@@ -16205,7 +16289,7 @@
         <v>1022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>13</v>
@@ -16227,15 +16311,15 @@
         <v>13</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>1351</v>
+        <v>1494</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="16"/>
       <c r="H25" s="15" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75">
@@ -16243,7 +16327,7 @@
         <v>1024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>13</v>
@@ -16259,7 +16343,7 @@
         <v>1025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>13</v>
@@ -16275,7 +16359,7 @@
         <v>1026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>13</v>
@@ -16291,7 +16375,7 @@
         <v>1027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>13</v>
@@ -16307,7 +16391,7 @@
         <v>1028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>13</v>
@@ -16323,7 +16407,7 @@
         <v>1029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>13</v>
@@ -16339,7 +16423,7 @@
         <v>1030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>13</v>
@@ -16355,22 +16439,22 @@
         <v>1032</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>1362</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>1363</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>1365</v>
       </c>
       <c r="H33" s="5"/>
     </row>
@@ -16379,20 +16463,20 @@
         <v>1033</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="4" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="H34" s="5"/>
     </row>
@@ -16401,23 +16485,23 @@
         <v>1034</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>713</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="18" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75">
@@ -16425,23 +16509,23 @@
         <v>1035</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>713</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="18" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75">
@@ -16449,25 +16533,25 @@
         <v>1036</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>713</v>
       </c>
       <c r="D37" s="15" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G37" s="16" t="s">
         <v>1379</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="H37" s="5" t="s">
         <v>1380</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>1381</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>1382</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75">
@@ -16475,25 +16559,25 @@
         <v>1037</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>713</v>
       </c>
       <c r="D38" s="15" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>1385</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>1386</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>1387</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>1388</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75">
@@ -16501,23 +16585,23 @@
         <v>1038</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>713</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="18" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75">
@@ -16525,7 +16609,7 @@
         <v>1039</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="C40" s="19" t="s">
         <v>1118</v>
@@ -16536,7 +16620,7 @@
         <v>1040</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="C41" s="19" t="s">
         <v>1118</v>
@@ -16547,7 +16631,7 @@
         <v>1041</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="C42" s="19" t="s">
         <v>1118</v>
@@ -16558,7 +16642,7 @@
         <v>1042</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="C43" s="19" t="s">
         <v>1118</v>
@@ -16569,7 +16653,7 @@
         <v>1043</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="C44" s="19" t="s">
         <v>1118</v>
@@ -16580,7 +16664,7 @@
         <v>1044</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="C45" s="19" t="s">
         <v>1118</v>
@@ -16591,7 +16675,7 @@
         <v>1045</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="C46" s="19" t="s">
         <v>1118</v>
@@ -16602,7 +16686,7 @@
         <v>1046</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="C47" s="19" t="s">
         <v>1118</v>
@@ -16613,7 +16697,7 @@
         <v>1047</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="C48" s="19" t="s">
         <v>1118</v>
@@ -16624,7 +16708,7 @@
         <v>1048</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="C49" s="19" t="s">
         <v>1118</v>
@@ -16635,7 +16719,7 @@
         <v>1049</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="C50" s="19" t="s">
         <v>1118</v>
@@ -16646,7 +16730,7 @@
         <v>1050</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="C51" s="19" t="s">
         <v>1118</v>
@@ -16657,7 +16741,7 @@
         <v>1051</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="C52" s="19" t="s">
         <v>1118</v>
@@ -16702,22 +16786,22 @@
         <v>1302</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>1407</v>
+      <c r="B2" s="11" t="s">
+        <v>1496</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="16" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="F2" s="16"/>
     </row>
@@ -16725,15 +16809,15 @@
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>1409</v>
+      <c r="B3" s="11" t="s">
+        <v>1497</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="16" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="F3" s="16"/>
     </row>
@@ -16741,15 +16825,15 @@
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>1411</v>
+      <c r="B4" s="11" t="s">
+        <v>1498</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="16" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="F4" s="16"/>
     </row>
@@ -16757,8 +16841,8 @@
       <c r="A5" s="2">
         <v>2013</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>1413</v>
+      <c r="B5" s="11" t="s">
+        <v>1499</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>13</v>
@@ -16771,8 +16855,8 @@
       <c r="A6" s="2">
         <v>2014</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>1414</v>
+      <c r="B6" s="11" t="s">
+        <v>1500</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>13</v>
@@ -16785,8 +16869,8 @@
       <c r="A7" s="2">
         <v>2017</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>1415</v>
+      <c r="B7" s="11" t="s">
+        <v>1501</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>13</v>
@@ -16799,15 +16883,15 @@
       <c r="A8" s="2">
         <v>2010</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>1416</v>
+      <c r="B8" s="11" t="s">
+        <v>1502</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="16" t="s">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="F8" s="16"/>
     </row>
@@ -16815,15 +16899,15 @@
       <c r="A9" s="2">
         <v>2008</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>1418</v>
+      <c r="B9" s="11" t="s">
+        <v>1503</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="16" t="s">
-        <v>1419</v>
+        <v>1407</v>
       </c>
       <c r="F9" s="16"/>
     </row>
@@ -16831,15 +16915,15 @@
       <c r="A10" s="2">
         <v>2021</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>1420</v>
+      <c r="B10" s="11" t="s">
+        <v>1504</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="16" t="s">
-        <v>1421</v>
+        <v>1408</v>
       </c>
       <c r="F10" s="16"/>
     </row>
@@ -16847,15 +16931,15 @@
       <c r="A11" s="2">
         <v>2022</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>1422</v>
+      <c r="B11" s="11" t="s">
+        <v>1505</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="16" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
       <c r="F11" s="16"/>
     </row>
@@ -16863,8 +16947,8 @@
       <c r="A12" s="2">
         <v>2012</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>1424</v>
+      <c r="B12" s="11" t="s">
+        <v>1506</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>13</v>
@@ -16877,8 +16961,8 @@
       <c r="A13" s="2">
         <v>2011</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>1425</v>
+      <c r="B13" s="11" t="s">
+        <v>1507</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>13</v>
@@ -16891,8 +16975,8 @@
       <c r="A14" s="2">
         <v>2015</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>1426</v>
+      <c r="B14" s="11" t="s">
+        <v>1508</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>13</v>
@@ -16905,8 +16989,8 @@
       <c r="A15" s="2">
         <v>2016</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>1427</v>
+      <c r="B15" s="11" t="s">
+        <v>1509</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>13</v>
@@ -16919,8 +17003,8 @@
       <c r="A16" s="2">
         <v>2023</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>1428</v>
+      <c r="B16" s="11" t="s">
+        <v>1510</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>13</v>
@@ -16933,15 +17017,15 @@
       <c r="A17" s="2">
         <v>2024</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>1429</v>
+      <c r="B17" s="11" t="s">
+        <v>1511</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="16" t="s">
-        <v>1430</v>
+        <v>1410</v>
       </c>
       <c r="F17" s="16"/>
     </row>
@@ -16949,355 +17033,355 @@
       <c r="A18" s="2">
         <v>2020</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>1431</v>
+      <c r="B18" s="11" t="s">
+        <v>1512</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1432</v>
+        <v>1411</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>1433</v>
+        <v>1412</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>1434</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75">
       <c r="A19" s="1">
         <v>2003</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>1435</v>
+      <c r="B19" s="11" t="s">
+        <v>1414</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1436</v>
+        <v>1415</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>1437</v>
+        <v>1416</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>1438</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75">
       <c r="A20" s="2">
         <v>2004</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>1439</v>
+      <c r="B20" s="11" t="s">
+        <v>1513</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>1440</v>
+        <v>1418</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>1441</v>
+        <v>1419</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>1442</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>1443</v>
+      <c r="B21" s="11" t="s">
+        <v>1514</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1444</v>
+        <v>1421</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>1445</v>
+        <v>1422</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>1446</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>1447</v>
+      <c r="B22" s="11" t="s">
+        <v>1515</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1448</v>
+        <v>1424</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>1449</v>
+        <v>1425</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>1450</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75">
       <c r="A23" s="2">
         <v>2018</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>1451</v>
+      <c r="B23" s="11" t="s">
+        <v>1516</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1452</v>
+        <v>1427</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1453</v>
+        <v>1428</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>1454</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75">
       <c r="A24" s="2">
         <v>2009</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>1455</v>
+      <c r="B24" s="11" t="s">
+        <v>1517</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1456</v>
+        <v>1430</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1456</v>
+        <v>1430</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>1457</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75">
       <c r="A25" s="2">
         <v>2025</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>1458</v>
+      <c r="B25" s="11" t="s">
+        <v>1518</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>1459</v>
+        <v>1432</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>1460</v>
+        <v>1433</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>1461</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75">
       <c r="A26" s="2">
         <v>2007</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>1462</v>
+      <c r="B26" s="11" t="s">
+        <v>1519</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>1463</v>
+        <v>1435</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>1464</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75">
       <c r="A27" s="2">
         <v>2019</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>1465</v>
+      <c r="B27" s="11" t="s">
+        <v>1520</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>1466</v>
+        <v>1437</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>1467</v>
+        <v>1438</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>1468</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75">
       <c r="A28" s="2">
         <v>2031</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>1469</v>
+      <c r="B28" s="11" t="s">
+        <v>1521</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>713</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1470</v>
+        <v>1440</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>1471</v>
+        <v>1441</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>1472</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75">
       <c r="A29" s="2">
         <v>2030</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>1473</v>
+      <c r="B29" s="11" t="s">
+        <v>1522</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>713</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1474</v>
+        <v>1443</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>1475</v>
+        <v>1444</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>1472</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75">
       <c r="A30" s="2">
         <v>2033</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>1476</v>
+      <c r="B30" s="11" t="s">
+        <v>1523</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>713</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1477</v>
+        <v>1445</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>1478</v>
+        <v>1446</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>1472</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75">
       <c r="A31" s="2">
         <v>2032</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>1479</v>
+      <c r="B31" s="11" t="s">
+        <v>1524</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>713</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1480</v>
+        <v>1447</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1481</v>
+        <v>1448</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>1482</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75">
       <c r="A32" s="2">
         <v>2026</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>1483</v>
+      <c r="B32" s="11" t="s">
+        <v>1525</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>713</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1484</v>
+        <v>1450</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>1485</v>
+        <v>1451</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>1486</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75">
       <c r="A33" s="2">
         <v>2027</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>1487</v>
+      <c r="B33" s="11" t="s">
+        <v>1526</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>713</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1488</v>
+        <v>1453</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>1489</v>
+        <v>1454</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>1486</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75">
       <c r="A34" s="2">
         <v>2029</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>1490</v>
+      <c r="B34" s="11" t="s">
+        <v>1527</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>713</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1491</v>
+        <v>1455</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>1492</v>
+        <v>1456</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>1493</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75">
       <c r="A35" s="2">
         <v>2028</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>1494</v>
+      <c r="B35" s="11" t="s">
+        <v>1528</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>713</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="16" t="s">
-        <v>1495</v>
+        <v>1458</v>
       </c>
       <c r="F35" s="16"/>
     </row>
@@ -17305,8 +17389,8 @@
       <c r="A36" s="2">
         <v>2043</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>1496</v>
+      <c r="B36" s="28" t="s">
+        <v>1529</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>1118</v>
@@ -17319,15 +17403,15 @@
       <c r="A37" s="2">
         <v>2040</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>1497</v>
+      <c r="B37" s="11" t="s">
+        <v>1530</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D37" s="16"/>
       <c r="E37" s="16" t="s">
-        <v>1498</v>
+        <v>1459</v>
       </c>
       <c r="F37" s="16"/>
     </row>
@@ -17335,15 +17419,15 @@
       <c r="A38" s="2">
         <v>2035</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>1499</v>
+      <c r="B38" s="11" t="s">
+        <v>1531</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="16" t="s">
-        <v>1500</v>
+        <v>1460</v>
       </c>
       <c r="F38" s="16"/>
     </row>
@@ -17351,8 +17435,8 @@
       <c r="A39" s="2">
         <v>2041</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>1501</v>
+      <c r="B39" s="11" t="s">
+        <v>1532</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>1118</v>
@@ -17365,15 +17449,15 @@
       <c r="A40" s="2">
         <v>2042</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>1502</v>
+      <c r="B40" s="11" t="s">
+        <v>1533</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="16" t="s">
-        <v>1503</v>
+        <v>1461</v>
       </c>
       <c r="F40" s="16"/>
     </row>
@@ -17381,15 +17465,15 @@
       <c r="A41" s="2">
         <v>2044</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>1504</v>
+      <c r="B41" s="11" t="s">
+        <v>1534</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D41" s="16"/>
       <c r="E41" s="16" t="s">
-        <v>1505</v>
+        <v>1462</v>
       </c>
       <c r="F41" s="16"/>
     </row>
@@ -17397,8 +17481,8 @@
       <c r="A42" s="2">
         <v>2036</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>1506</v>
+      <c r="B42" s="11" t="s">
+        <v>1535</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>1118</v>
@@ -17411,15 +17495,15 @@
       <c r="A43" s="2">
         <v>2034</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>1507</v>
+      <c r="B43" s="11" t="s">
+        <v>1536</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16" t="s">
-        <v>1508</v>
+        <v>1463</v>
       </c>
       <c r="F43" s="16"/>
     </row>
@@ -17427,15 +17511,15 @@
       <c r="A44" s="2">
         <v>2037</v>
       </c>
-      <c r="B44" s="16" t="s">
-        <v>1509</v>
+      <c r="B44" s="11" t="s">
+        <v>1537</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16" t="s">
-        <v>1510</v>
+        <v>1464</v>
       </c>
       <c r="F44" s="16"/>
     </row>
@@ -17443,15 +17527,15 @@
       <c r="A45" s="2">
         <v>2038</v>
       </c>
-      <c r="B45" s="16" t="s">
-        <v>1511</v>
+      <c r="B45" s="11" t="s">
+        <v>1538</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="16" t="s">
-        <v>1512</v>
+        <v>1465</v>
       </c>
       <c r="F45" s="16"/>
     </row>
@@ -17459,15 +17543,15 @@
       <c r="A46" s="2">
         <v>2039</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>1513</v>
+      <c r="B46" s="11" t="s">
+        <v>1539</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="16" t="s">
-        <v>1514</v>
+        <v>1466</v>
       </c>
       <c r="F46" s="16"/>
     </row>
@@ -17475,15 +17559,15 @@
       <c r="A47" s="2">
         <v>2045</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>1515</v>
+      <c r="B47" s="11" t="s">
+        <v>1540</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>1118</v>
       </c>
       <c r="D47" s="16"/>
       <c r="E47" s="16" t="s">
-        <v>1516</v>
+        <v>1467</v>
       </c>
       <c r="F47" s="16"/>
     </row>
@@ -17512,55 +17596,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1517</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>1518</v>
+        <v>1469</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1519</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>1520</v>
+        <v>1471</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1521</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>1522</v>
+        <v>1473</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1523</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>1524</v>
+        <v>1475</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1525</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>1526</v>
+        <v>1477</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1527</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>1528</v>
+        <v>1479</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1529</v>
+        <v>1480</v>
       </c>
     </row>
   </sheetData>
@@ -17586,12 +17670,12 @@
         <v>1301</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>1530</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>1531</v>
+        <v>1482</v>
       </c>
       <c r="B2" s="24" t="b">
         <f>FALSE()</f>
